--- a/healthcare_surveys/017_care_continuity_improvement_project_registration_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/017_care_continuity_improvement_project_registration_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -900,8 +900,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -929,12 +929,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'quality_improvement_(qi)',_'value':_'quality_improvement'}</t>
+          <t>quality_improvement_(qi)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Quality Improvement (QI)', 'value': 'quality_improvement'}</t>
+          <t>Quality Improvement (QI)</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'patient_safety',_'value':_'patient_safety'}</t>
+          <t>patient_safety</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Patient Safety', 'value': 'patient_safety'}</t>
+          <t>Patient Safety</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'staff_education/training',_'value':_'staff_education'}</t>
+          <t>staff_education/training</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Staff Education/Training', 'value': 'staff_education'}</t>
+          <t>Staff Education/Training</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'technology_implementation',_'value':_'technology'}</t>
+          <t>technology_implementation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Technology Implementation', 'value': 'technology'}</t>
+          <t>Technology Implementation</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'process_optimization',_'value':_'process_optimization'}</t>
+          <t>process_optimization</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Process Optimization', 'value': 'process_optimization'}</t>
+          <t>Process Optimization</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'authorized_and_registered',_'value':_'authorized'}</t>
+          <t>authorized_and_registered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Authorized and Registered', 'value': 'authorized'}</t>
+          <t>Authorized and Registered</t>
         </is>
       </c>
     </row>
